--- a/pabi_account_report/xlsx_template/xlsx_report_sla_procurement.xlsx
+++ b/pabi_account_report/xlsx_template/xlsx_report_sla_procurement.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="990" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="SLA Procurement Report" sheetId="1" state="visible" r:id="rId2"/>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Document Header Text</t>
   </si>
   <si>
-    <t xml:space="preserve">Suppiler Code</t>
+    <t xml:space="preserve">Supplier Code</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier Name</t>
@@ -1792,29 +1792,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="1:11"/>
-  <sheetFormatPr defaultRowHeight="12.8"/>
+  <dimension ref="A1:AMJ11"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="1" width="17.1632653061224"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="2" width="23.0408163265306"/>
-    <col collapsed="false" hidden="false" max="3" min="3" style="2" width="20.6377551020408"/>
-    <col collapsed="false" hidden="false" max="4" min="4" style="3" width="20.5204081632653"/>
-    <col collapsed="false" hidden="false" max="5" min="5" style="2" width="20.6377551020408"/>
-    <col collapsed="false" hidden="false" max="6" min="6" style="1" width="17.0459183673469"/>
-    <col collapsed="false" hidden="false" max="7" min="7" style="2" width="17.0459183673469"/>
-    <col collapsed="false" hidden="false" max="8" min="8" style="2" width="16.9183673469388"/>
-    <col collapsed="false" hidden="false" max="9" min="9" style="2" width="20.4030612244898"/>
-    <col collapsed="false" hidden="false" max="10" min="10" style="2" width="15"/>
-    <col collapsed="false" hidden="false" max="11" min="11" style="3" width="18"/>
-    <col collapsed="false" hidden="false" max="12" min="12" style="4" width="18"/>
-    <col collapsed="false" hidden="false" max="13" min="13" style="5" width="15.234693877551"/>
-    <col collapsed="false" hidden="false" max="14" min="14" style="6" width="13.4336734693878"/>
-    <col collapsed="false" hidden="false" max="15" min="15" style="2" width="20.0408163265306"/>
-    <col collapsed="false" hidden="false" max="16" min="16" style="5" width="13.8061224489796"/>
-    <col collapsed="false" hidden="false" max="17" min="17" style="6" width="13.8061224489796"/>
-    <col collapsed="false" hidden="false" max="18" min="18" style="7" width="14.280612244898"/>
-    <col collapsed="false" hidden="false" max="19" min="19" style="7" width="11.4030612244898"/>
-    <col collapsed="false" hidden="false" max="1025" min="20" style="7" width="11.5204081632653"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="2" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="4" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="5" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="5" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="6" width="21.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="18" style="7" width="21.68"/>
   </cols>
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11134,7 +11128,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
@@ -11148,11 +11142,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B459"/>
-  <sheetFormatPr defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="22" width="24.9540816326531"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="22" width="22.4336734693878"/>
-    <col collapsed="false" hidden="false" max="1025" min="3" style="0" width="11.5204081632653"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="25.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="22" width="22.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="3" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14217,7 +14211,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="false" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
